--- a/scripts/recalc/edges.xlsx
+++ b/scripts/recalc/edges.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Output" sheetId="2" r:id="rIdFrazaro2"/>
   </sheets>
   <definedNames>
-    <definedName name="Frazaro.Build">"Frazaro 0.8.0; sentences sha256:BD2AF95AE8DED82D9164DAD53CD3EDB548FB43196B5B430549478A172370ABD8 over 918 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
+    <definedName name="Frazaro.Build">"Frazaro 0.8.1; sentences sha256:BD2AF95AE8DED82D9164DAD53CD3EDB548FB43196B5B430549478A172370ABD8 over 918 non-whitespace bytes; prelude sha256:887F55C46AA71563EE5DE0F74E3D4DB1C0022986248AD1FBF8A7A63711AC508C over 27033 non-whitespace bytes; phrasebook 1 sha256:5E5FF4121AA83D783E926C1A78B8E8C7C45BFE1E1184340F8D93A0285DDCB949 over 167902 non-whitespace bytes"</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -389,8 +389,9 @@
           <t xml:space="preserve">TRUE</t>
         </is>
       </c>
-      <c r="C1" s="0">
+      <c r="C1" s="0" t="str">
         <f>10^14&amp;""</f>
+        <v>100000000000000</v>
       </c>
     </row>
     <row r="2">
@@ -399,8 +400,9 @@
           <t xml:space="preserve">false</t>
         </is>
       </c>
-      <c r="C2" s="0">
+      <c r="C2" s="0" t="str">
         <f>10^15&amp;""</f>
+        <v>1E+15</v>
       </c>
     </row>
     <row r="3">
@@ -409,73 +411,87 @@
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C3" s="0">
+      <c r="C3" s="0" t="str">
         <f>10^15-1&amp;""</f>
+        <v>999999999999999</v>
       </c>
     </row>
     <row r="4">
-      <c r="C4" s="0">
+      <c r="C4" s="0" t="str">
         <f>2^57&amp;""</f>
+        <v>1.44115188075856E+17</v>
       </c>
     </row>
     <row r="5">
-      <c r="C5" s="0">
+      <c r="C5" s="0" t="str">
         <f>10^-14&amp;""</f>
+        <v>0.00000000000001</v>
       </c>
     </row>
     <row r="6">
-      <c r="C6" s="0">
+      <c r="C6" s="0" t="str">
         <f>10^-15&amp;""</f>
+        <v>1E-15</v>
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="0">
+      <c r="C7" s="0" t="str">
         <f>1/3*10^-5&amp;""</f>
+        <v>0.00000333333333333333</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="0">
+      <c r="C8" s="0" t="str">
         <f>1/3*10^-10&amp;""</f>
+        <v>0.0000000000333333333333333</v>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="0">
+      <c r="C9" s="0" t="str">
         <f>-0.0000001&amp;""</f>
+        <v>-0.0000001</v>
       </c>
     </row>
     <row r="10">
-      <c r="C10" s="0">
+      <c r="C10" s="0" t="str">
         <f>1/7*10^6&amp;""</f>
+        <v>142857.142857143</v>
       </c>
     </row>
     <row r="11">
-      <c r="C11" s="0">
+      <c r="C11" s="0" t="str">
         <f>2^0.5&amp;""</f>
+        <v>1.4142135623731</v>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="0">
+      <c r="C12" s="0" t="b">
         <f>NOT(A1)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="0" cm="1">
         <f t="array" ref="C13">_xlfn.IFS(A1,1,TRUE,2)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="0">
         <f>IF(A2,1,2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="0">
+      <c r="C15" s="0" t="e">
         <f>IF(A3,1,2)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="0">
+      <c r="C16" s="0" t="e">
         <f>OR(A1)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>
